--- a/output/laminas_comunales/comunal_o_ocup_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,37 +384,37 @@
         </is>
       </c>
       <c r="C2">
-        <v>39.3152229992581</v>
+        <v>54.8080893891662</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.1286032258839</v>
+        <v>53.0448717948718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.2700553741303</v>
+        <v>50.6534424853065</v>
       </c>
     </row>
     <row r="5">
@@ -429,37 +429,682 @@
         </is>
       </c>
       <c r="C5">
-        <v>32.6815995950392</v>
+        <v>50.0175808720113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C6">
-        <v>26.1248345831495</v>
+        <v>49.8959584465938</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>48.6431426814268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>48.6056027183236</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>46.0911926223172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>45.1391180028593</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>44.7919598461394</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>44.6676318665184</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>43.8734836979958</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>43.1868294958233</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.177033492823</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>39.3152229992581</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>38.8946426031748</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>38.1321370309951</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>38.1286032258839</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>36.923520368947</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>36.2700553741303</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>1402</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Camiña</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C22">
+        <v>34.7985347985348</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>34.7850678733032</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>34.7174471336231</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>33.1895518811407</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>33.0045628795748</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>32.6815995950392</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>32.4572227706482</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>32.1042225598259</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>31.9106652786978</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>31.771511123505</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>30.0957207207207</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>29.8333053233057</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>28.5415103775944</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>27.5354752342704</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>26.6666666666667</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>26.1248345831495</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>23.8042678440029</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>23.4567901234568</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>21.7836257309942</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C42">
         <v>20.4537237888648</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>17.2174840085288</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>14.2232367341538</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>13.3753289827049</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>13.0871094558245</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>12.2960372960373</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>7.87292817679558</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>7.83176214648296</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>3.998778998779</v>
       </c>
     </row>
   </sheetData>
